--- a/output/pdf_financials_xlsx/GREY.xlsx
+++ b/output/pdf_financials_xlsx/GREY.xlsx
@@ -715,16 +715,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>6.054356</v>
+        <v>-6.054356</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>6.7812</v>
+        <v>-6.7812</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.502982</v>
+        <v>-0.502982</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.717055</v>
+        <v>-1.717055</v>
       </c>
     </row>
     <row r="17">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>6.054356</v>
+        <v>-6.054356</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>6.7812</v>
+        <v>-6.7812</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.502982</v>
+        <v>-0.502982</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.717055</v>
+        <v>-1.717055</v>
       </c>
     </row>
     <row r="21">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>6.054356</v>
+        <v>-6.054356</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>6.7812</v>
+        <v>-6.7812</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.502982</v>
+        <v>-0.502982</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.717055</v>
+        <v>-1.717055</v>
       </c>
     </row>
     <row r="24">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>6.054356</v>
+        <v>-6.054356</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>6.7812</v>
+        <v>-6.7812</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.502982</v>
+        <v>-0.502982</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.717055</v>
+        <v>-1.717055</v>
       </c>
     </row>
     <row r="28">
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>6.054356</v>
+        <v>-6.054356</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>6.7812</v>
+        <v>-6.7812</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.502982</v>
+        <v>-0.502982</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.717055</v>
+        <v>-1.717055</v>
       </c>
     </row>
     <row r="30">
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2235,16 +2235,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.733188</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.148624</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.409675</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.805589</v>
       </c>
     </row>
     <row r="93">
@@ -3642,7 +3642,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -4100,7 +4104,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -4278,7 +4286,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>3.733188</v>
       </c>
@@ -8288,10 +8300,10 @@
         </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.502982</v>
+        <v>-0.502982</v>
       </c>
       <c r="H147" s="5" t="n">
-        <v>1.717055</v>
+        <v>-1.717055</v>
       </c>
     </row>
     <row r="148">
@@ -8360,10 +8372,10 @@
         </is>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.511093</v>
+        <v>-0.511093</v>
       </c>
       <c r="H149" s="5" t="n">
-        <v>1.717322</v>
+        <v>-1.717322</v>
       </c>
     </row>
     <row r="150">
@@ -8744,13 +8756,13 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>6.054356</v>
+        <v>-6.054356</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>6.7812</v>
+        <v>-6.7812</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.502982</v>
+        <v>-0.502982</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -8812,13 +8824,13 @@
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>6.076618</v>
+        <v>-6.076618</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>6.776449</v>
+        <v>-6.776449</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.511093</v>
+        <v>-0.511093</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GREY.xlsx
+++ b/output/pdf_financials_xlsx/GREY.xlsx
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002078</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002097</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001368</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000739</v>
       </c>
     </row>
     <row r="13">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.054356</v>
+        <v>-6.052278</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-6.7812</v>
+        <v>-6.779103</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.502982</v>
+        <v>-0.501614</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.717055</v>
+        <v>-1.716316</v>
       </c>
     </row>
     <row r="28">
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.054356</v>
+        <v>-6.052278</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.7812</v>
+        <v>-6.779103</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.502982</v>
+        <v>-0.501614</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.717055</v>
+        <v>-1.716316</v>
       </c>
     </row>
     <row r="30">
@@ -1110,7 +1110,7 @@
         <v>0.596198</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.176501</v>
       </c>
     </row>
     <row r="35">
@@ -1148,7 +1148,7 @@
         <v>0.596198</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.176501</v>
       </c>
     </row>
     <row r="37">
@@ -1376,7 +1376,7 @@
         <v>0.126879</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.537434</v>
+        <v>0.360933</v>
       </c>
     </row>
     <row r="49">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">

--- a/output/pdf_financials_xlsx/GREY.xlsx
+++ b/output/pdf_financials_xlsx/GREY.xlsx
@@ -4840,7 +4840,11 @@
           <t>Additions of intangible assets</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -7530,7 +7534,11 @@
           <t>Additions of intangible assets</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E126" s="5" t="n">
         <v>-0.144608</v>
       </c>
